--- a/branches/issue-82/StructureDefinition-PSSPatient.xlsx
+++ b/branches/issue-82/StructureDefinition-PSSPatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-30T14:13:57+00:00</t>
+    <t>2025-04-30T14:16:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
